--- a/images/document/OneDrive_1_9-17-2026/Tổ Khai thác - GRI 302-4 - Giảm tiêu thụ năng lượng.xlsx
+++ b/images/document/OneDrive_1_9-17-2026/Tổ Khai thác - GRI 302-4 - Giảm tiêu thụ năng lượng.xlsx
@@ -1,126 +1,311 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d39b8747432be571/Work/04. Company/Synodus/GOV/01.VNA/VNA/images/document/OneDrive_1_9-17-2026/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F235327383A280BDD76168A6B2EBDB7844D543A5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E0AA98D-700B-4B41-A3D5-0816DC92CA14}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GRI 302-4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mô tả trường dữ liệu" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Script" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Template" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Template" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GRI 302-4" sheetId="1" r:id="rId1"/>
+    <sheet name="Mô tả trường dữ liệu" sheetId="2" r:id="rId2"/>
+    <sheet name="SQL Script" sheetId="3" r:id="rId3"/>
+    <sheet name="Import Template" sheetId="4" r:id="rId4"/>
+    <sheet name="Export Template" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+  <si>
+    <t>Kỳ báo cáo (Snapshot Date)</t>
+  </si>
+  <si>
+    <t>Tổng nhiên liệu tiết kiệm thực tế (Actual saving fuel) (kg)</t>
+  </si>
+  <si>
+    <t>Mục tiêu tiết kiệm nhiên liệu (Target saving fuel) (kg)</t>
+  </si>
+  <si>
+    <t>Người tạo (Created by)</t>
+  </si>
+  <si>
+    <t>[Bắt buộc] Định dạng YYYY-MM. Mỗi tháng chỉ nhập 1 bản ghi duy nhất. Thời gian nhập: ngày 15-20 hàng tháng.</t>
+  </si>
+  <si>
+    <t>[Bắt buộc] Kiểu số thực (Decimal/Float). Giá trị &gt;= 0.</t>
+  </si>
+  <si>
+    <t>ID hoặc Username của người thao tác (Hệ thống có thể tự động lấy theo phiên đăng nhập).</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>admin_khai_thac</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>=&gt; Bỏ cột này</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Tên trường (Field Name)</t>
+  </si>
+  <si>
+    <t>Kiểu dữ liệu (Data Type)</t>
+  </si>
+  <si>
+    <t>Mô tả (Description)</t>
+  </si>
+  <si>
+    <t>Quy tắc ràng buộc (Validation Rules)</t>
+  </si>
+  <si>
+    <t>Ghi chú (Note)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snapshot_date </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATE </t>
+  </si>
+  <si>
+    <t>Kỳ báo cáo theo tháng, thể hiện tháng mà số liệu tiết kiệm nhiên liệu được ghi nhận</t>
+  </si>
+  <si>
+    <t>- Bắt buộc (NOT NULL)
+- Định dạng YYYY-MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actual_saving_fuel_kg </t>
+  </si>
+  <si>
+    <t>DECIMAL</t>
+  </si>
+  <si>
+    <t>Tổng khối lượng nhiên liệu tiết kiệm thực tế trong kỳ báo cáo, đơn vị kg</t>
+  </si>
+  <si>
+    <t>- Bắt buộc (NOT NULL)
+- &gt;= 0
+- Kiểu số thực, cho phép phần thập phân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_saving_fuel_kg </t>
+  </si>
+  <si>
+    <t>Mục tiêu/chỉ tiêu tiết kiệm nhiên liệu được đặt ra cho kỳ báo cáo, đơn vị kg</t>
+  </si>
+  <si>
+    <t>Bỏ cột này</t>
+  </si>
+  <si>
+    <t xml:space="preserve">created_by </t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>ID hoặc username của người thực hiện nhập liệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">created_at </t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>Dấu thời gian hệ thống ghi nhận khi bản ghi được tạo</t>
+  </si>
+  <si>
+    <t>GHI CHÚ</t>
+  </si>
+  <si>
+    <t>Không thấy cột Validation Rules trong ảnh nên không thêm NOT NULL/PRIMARY KEY. Catalog/schema giả định "oracle-warehouse".nzwh giống các file trước - đổi lại nếu khác.</t>
+  </si>
+  <si>
+    <t>1. CREATE TABLE f_ops_supp_supplier</t>
+  </si>
+  <si>
+    <t>CREATE TABLE "oracle-warehouse".nzwh.f_ops_supp_supplier (
+    supplier_name VARCHAR,
+    supplier_type VARCHAR,
+    supplier_code VARCHAR,
+    sustainability_commitment VARCHAR,
+    commitment_effective_date DATE
+);</t>
+  </si>
+  <si>
+    <t>2. CREATE TABLE f_ops_supp_contract</t>
+  </si>
+  <si>
+    <t>CREATE TABLE "oracle-warehouse".nzwh.f_ops_supp_contract (
+    contract_name VARCHAR,
+    contract_code VARCHAR,
+    supplier_code VARCHAR,
+    contract_start_date DATE,
+    contract_end_date DATE
+);</t>
+  </si>
+  <si>
+    <t>3. GRI 302-4 - Tiết kiệm nhiên liệu (bảng: f_ops_fuel_saving)</t>
+  </si>
+  <si>
+    <t>Lưu ý: DECIMAL giả định (18,2) (sheet mô tả không ghi rõ precision). snapshot_date chỉ có YYYY-MM nên quy ước lấy ngày 01 hàng tháng. Cột created_at không có sẵn dữ liệu mẫu (do hệ thống tự sinh khi insert thực tế) nên tạm bỏ qua trong câu INSERT.</t>
+  </si>
+  <si>
+    <t>CREATE TABLE "oracle-warehouse".nzwh.f_ops_fuel_saving (
+    snapshot_date DATE NOT NULL,
+    actual_saving_fuel_kg DECIMAL(18,2) NOT NULL,
+    target_saving_fuel_kg DECIMAL(18,2) NOT NULL,
+    created_by VARCHAR,
+    created_at TIMESTAMP
+);</t>
+  </si>
+  <si>
+    <t>INSERT INTO "oracle-warehouse".nzwh.f_ops_fuel_saving (snapshot_date, actual_saving_fuel_kg, target_saving_fuel_kg, created_by) VALUES
+(DATE '2026-01-01', 152500.50, 150000.00, 'admin_khai_thac'),
+(DATE '2026-02-01', 148000.00, 150000.00, 'admin_khai_thac'),
+(DATE '2026-03-01', 161200.75, 155000.00, 'admin_khai_thac'),
+(DATE '2026-04-01', 155000.00, 155000.00, 'admin_khai_thac');</t>
+  </si>
+  <si>
+    <t>Kỳ báo cáo (snapshot_date)</t>
+  </si>
+  <si>
+    <t>Tổng khối lượng nhiên liệu tiết kiệm thực tế (actual_saving_fuel_kg)</t>
+  </si>
+  <si>
+    <t>ID bản ghi</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="14">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <i val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <i val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Consolas"/>
-      <color theme="1"/>
-      <sz val="10"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color rgb="FF1F1F1F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Aptos Narrow"/>
-      <i val="1"/>
-      <color rgb="FF1F1F1F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Aptos Narrow"/>
-      <color rgb="FF1F1F1F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -145,14 +330,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000556E"/>
-        <bgColor rgb="0000556E"/>
+        <fgColor rgb="FF00556E"/>
+        <bgColor rgb="FF00556E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="FF1E3A8A"/>
+        <bgColor rgb="FF1E3A8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -331,188 +516,130 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="34">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -832,146 +959,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="22.140625" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="25.140625" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="22.1640625" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="25.1640625" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="43.5" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Kỳ báo cáo (Snapshot Date)</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Tổng nhiên liệu tiết kiệm thực tế (Actual saving fuel) (kg)</t>
-        </is>
-      </c>
-      <c r="C1" s="16" t="inlineStr">
-        <is>
-          <t>Mục tiêu tiết kiệm nhiên liệu (Target saving fuel) (kg)</t>
-        </is>
-      </c>
-      <c r="D1" s="17" t="inlineStr">
-        <is>
-          <t>Người tạo (Created by)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="88.5" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>[Bắt buộc] Định dạng YYYY-MM. Mỗi tháng chỉ nhập 1 bản ghi duy nhất. Thời gian nhập: ngày 15-20 hàng tháng.</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
-        <is>
-          <t>[Bắt buộc] Kiểu số thực (Decimal/Float). Giá trị &gt;= 0.</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
-          <t>[Bắt buộc] Kiểu số thực (Decimal/Float). Giá trị &gt;= 0.</t>
-        </is>
-      </c>
-      <c r="D2" s="21" t="inlineStr">
-        <is>
-          <t>ID hoặc Username của người thao tác (Hệ thống có thể tự động lấy theo phiên đăng nhập).</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="n">
+    <row r="1" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="23">
         <v>152500.5</v>
       </c>
-      <c r="C3" s="24" t="n">
+      <c r="C3" s="24">
         <v>150000</v>
       </c>
-      <c r="D3" s="25" t="inlineStr">
-        <is>
-          <t>admin_khai_thac</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="n">
+      <c r="D3" s="25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="23">
         <v>148000</v>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="24">
         <v>150000</v>
       </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>admin_khai_thac</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="n">
+      <c r="D4" s="25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="23">
         <v>161200.75</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="24">
         <v>155000</v>
       </c>
-      <c r="D5" s="25" t="inlineStr">
-        <is>
-          <t>admin_khai_thac</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="D5" s="25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="23">
         <v>155000</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="24">
         <v>155000</v>
       </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>admin_khai_thac</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="28" t="inlineStr">
-        <is>
-          <t>=&gt; Bỏ cột này</t>
-        </is>
-      </c>
-      <c r="D7" s="29" t="n"/>
+      <c r="D6" s="25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -979,178 +1068,119 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="24.7109375" customWidth="1" min="2" max="2"/>
-    <col width="23.7109375" customWidth="1" min="3" max="3"/>
-    <col width="20.7109375" customWidth="1" min="4" max="6"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
+    <col min="4" max="6" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Tên trường (Field Name)</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Kiểu dữ liệu (Data Type)</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Mô tả (Description)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Quy tắc ràng buộc (Validation Rules)</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Ghi chú (Note)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="57.75" customHeight="1">
-      <c r="A2" s="6" t="n">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">snapshot_date </t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DATE </t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Kỳ báo cáo theo tháng, thể hiện tháng mà số liệu tiết kiệm nhiên liệu được ghi nhận</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>- Bắt buộc (NOT NULL)
-- Định dạng YYYY-MM</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="57.75" customHeight="1">
-      <c r="A3" s="4" t="n">
+      <c r="B2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">actual_saving_fuel_kg </t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>DECIMAL</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Tổng khối lượng nhiên liệu tiết kiệm thực tế trong kỳ báo cáo, đơn vị kg</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>- Bắt buộc (NOT NULL)
-- &gt;= 0
-- Kiểu số thực, cho phép phần thập phân</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="57.75" customHeight="1">
-      <c r="A4" s="30" t="n">
+      <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="30">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">target_saving_fuel_kg </t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t>DECIMAL</t>
-        </is>
-      </c>
-      <c r="D4" s="30" t="inlineStr">
-        <is>
-          <t>Mục tiêu/chỉ tiêu tiết kiệm nhiên liệu được đặt ra cho kỳ báo cáo, đơn vị kg</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>- Bắt buộc (NOT NULL)
-- &gt;= 0
-- Kiểu số thực, cho phép phần thập phân</t>
-        </is>
-      </c>
-      <c r="F4" s="30" t="inlineStr">
-        <is>
-          <t>Bỏ cột này</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="43.5" customHeight="1">
-      <c r="A5" s="4" t="n">
+      <c r="B4" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">created_by </t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>ID hoặc username của người thực hiện nhập liệu</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="43.5" customHeight="1">
-      <c r="A6" t="n">
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">created_at </t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Dấu thời gian hệ thống ghi nhận khi bản ghi được tạo</t>
-        </is>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1159,113 +1189,67 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="118.140625" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="118.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>GHI CHÚ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Không thấy cột Validation Rules trong ảnh nên không thêm NOT NULL/PRIMARY KEY. Catalog/schema giả định "oracle-warehouse".nzwh giống các file trước - đổi lại nếu khác.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>1. CREATE TABLE f_ops_supp_supplier</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="90.75" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>CREATE TABLE "oracle-warehouse".nzwh.f_ops_supp_supplier (
-    supplier_name VARCHAR,
-    supplier_type VARCHAR,
-    supplier_code VARCHAR,
-    sustainability_commitment VARCHAR,
-    commitment_effective_date DATE
-);</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>2. CREATE TABLE f_ops_supp_contract</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90.75" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>CREATE TABLE "oracle-warehouse".nzwh.f_ops_supp_contract (
-    contract_name VARCHAR,
-    contract_code VARCHAR,
-    supplier_code VARCHAR,
-    contract_start_date DATE,
-    contract_end_date DATE
-);</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>3. GRI 302-4 - Tiết kiệm nhiên liệu (bảng: f_ops_fuel_saving)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25.5" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Lưu ý: DECIMAL giả định (18,2) (sheet mô tả không ghi rõ precision). snapshot_date chỉ có YYYY-MM nên quy ước lấy ngày 01 hàng tháng. Cột created_at không có sẵn dữ liệu mẫu (do hệ thống tự sinh khi insert thực tế) nên tạm bỏ qua trong câu INSERT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90.75" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>CREATE TABLE "oracle-warehouse".nzwh.f_ops_fuel_saving (
-    snapshot_date DATE NOT NULL,
-    actual_saving_fuel_kg DECIMAL(18,2) NOT NULL,
-    target_saving_fuel_kg DECIMAL(18,2) NOT NULL,
-    created_by VARCHAR,
-    created_at TIMESTAMP
-);</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="77.25" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>INSERT INTO "oracle-warehouse".nzwh.f_ops_fuel_saving (snapshot_date, actual_saving_fuel_kg, target_saving_fuel_kg, created_by) VALUES
-(DATE '2026-01-01', 152500.50, 150000.00, 'admin_khai_thac'),
-(DATE '2026-02-01', 148000.00, 150000.00, 'admin_khai_thac'),
-(DATE '2026-03-01', 161200.75, 155000.00, 'admin_khai_thac'),
-(DATE '2026-04-01', 155000.00, 155000.00, 'admin_khai_thac');</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11"/>
+    </row>
+    <row r="7" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="90.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" s="11"/>
+    </row>
+    <row r="14" spans="1:1" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1274,34 +1258,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="32" t="inlineStr">
-        <is>
-          <t>Kỳ báo cáo (snapshot_date)</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="inlineStr">
-        <is>
-          <t>Tổng khối lượng nhiên liệu tiết kiệm thực tế (actual_saving_fuel_kg)</t>
-        </is>
-      </c>
-      <c r="C1" s="32" t="inlineStr">
-        <is>
-          <t>Mục tiêu tiết kiệm nhiên liệu (target_saving_fuel_kg)</t>
-        </is>
+    <row r="1" spans="1:2" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1310,40 +1280,24 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
-        <is>
-          <t>ID bản ghi</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="inlineStr">
-        <is>
-          <t>Kỳ báo cáo (snapshot_date)</t>
-        </is>
-      </c>
-      <c r="C1" s="32" t="inlineStr">
-        <is>
-          <t>Tổng khối lượng nhiên liệu tiết kiệm thực tế (actual_saving_fuel_kg)</t>
-        </is>
-      </c>
-      <c r="D1" s="32" t="inlineStr">
-        <is>
-          <t>Mục tiêu tiết kiệm nhiên liệu (target_saving_fuel_kg)</t>
-        </is>
+    <row r="1" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
